--- a/deliverables/optimization_workbook.xlsx
+++ b/deliverables/optimization_workbook.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assortment" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ServiceLevel" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5774,6 +5775,750 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Forecast-uncertainty -&gt; service-level curve (illustrative cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Recommended target service level: 96%  |  expected fill rate 99.3%  |  total illustrative cost EUR 604/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>service_level</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>empirical_z</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>gaussian_z</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>safety_stock_units</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>safety_capital_eur</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>holding_cost_eur_month</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>expected_fill_rate</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>expected_stockout_units_month</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>expected_stockout_cost_eur_month</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>total_cost_eur_month</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="D5" t="n">
+        <v>223.52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13055.38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>247.87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.93835</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="I5" t="n">
+        <v>759.3099999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1007.17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.1246</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8779</v>
+      </c>
+      <c r="D6" t="n">
+        <v>230.19</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13444.79</v>
+      </c>
+      <c r="F6" t="n">
+        <v>255.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9412199999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="I6" t="n">
+        <v>724.05</v>
+      </c>
+      <c r="J6" t="n">
+        <v>979.3099999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.1559</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="D7" t="n">
+        <v>236.59</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13819.12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>262.37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.94384</v>
+      </c>
+      <c r="H7" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="I7" t="n">
+        <v>691.78</v>
+      </c>
+      <c r="J7" t="n">
+        <v>954.14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.2094</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="D8" t="n">
+        <v>247.55</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14459.03</v>
+      </c>
+      <c r="F8" t="n">
+        <v>274.52</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.94804</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>639.95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>914.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.2639</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15110.49</v>
+      </c>
+      <c r="F9" t="n">
+        <v>286.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.95211</v>
+      </c>
+      <c r="H9" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>589.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>876.79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.3188</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.0364</v>
+      </c>
+      <c r="D10" t="n">
+        <v>269.93</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15766.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>299.34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.95594</v>
+      </c>
+      <c r="H10" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="I10" t="n">
+        <v>542.71</v>
+      </c>
+      <c r="J10" t="n">
+        <v>842.04</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.3789</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.0803</v>
+      </c>
+      <c r="D11" t="n">
+        <v>282.24</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16485.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>312.99</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.95987</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="I11" t="n">
+        <v>494.23</v>
+      </c>
+      <c r="J11" t="n">
+        <v>807.22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.4351</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.1264</v>
+      </c>
+      <c r="D12" t="n">
+        <v>293.74</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17156.95</v>
+      </c>
+      <c r="F12" t="n">
+        <v>325.74</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.96331</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="I12" t="n">
+        <v>451.97</v>
+      </c>
+      <c r="J12" t="n">
+        <v>777.71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.5147</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="D13" t="n">
+        <v>310.03</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18108.59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.96777</v>
+      </c>
+      <c r="H13" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="I13" t="n">
+        <v>396.99</v>
+      </c>
+      <c r="J13" t="n">
+        <v>740.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.5647</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.2265</v>
+      </c>
+      <c r="D14" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18706.04</v>
+      </c>
+      <c r="F14" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.97036</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="I14" t="n">
+        <v>365.02</v>
+      </c>
+      <c r="J14" t="n">
+        <v>720.17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1.6551</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.2816</v>
+      </c>
+      <c r="D15" t="n">
+        <v>338.78</v>
+      </c>
+      <c r="E15" t="n">
+        <v>19787.37</v>
+      </c>
+      <c r="F15" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.97467</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>312.01</v>
+      </c>
+      <c r="J15" t="n">
+        <v>687.6900000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1.7199</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.3408</v>
+      </c>
+      <c r="D16" t="n">
+        <v>352.04</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20561.84</v>
+      </c>
+      <c r="F16" t="n">
+        <v>390.38</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.97744</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="I16" t="n">
+        <v>277.86</v>
+      </c>
+      <c r="J16" t="n">
+        <v>668.25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.8009</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.4051</v>
+      </c>
+      <c r="D17" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="E17" t="n">
+        <v>21530.37</v>
+      </c>
+      <c r="F17" t="n">
+        <v>408.77</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.98056</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="I17" t="n">
+        <v>239.41</v>
+      </c>
+      <c r="J17" t="n">
+        <v>648.1799999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1.8715</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.4758</v>
+      </c>
+      <c r="D18" t="n">
+        <v>383.06</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22374.09</v>
+      </c>
+      <c r="F18" t="n">
+        <v>424.79</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.98298</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="I18" t="n">
+        <v>209.65</v>
+      </c>
+      <c r="J18" t="n">
+        <v>634.4400000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.9958</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.5548</v>
+      </c>
+      <c r="D19" t="n">
+        <v>408.51</v>
+      </c>
+      <c r="E19" t="n">
+        <v>23860.27</v>
+      </c>
+      <c r="F19" t="n">
+        <v>453.01</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.98658</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I19" t="n">
+        <v>165.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>618.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2.153</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.6449</v>
+      </c>
+      <c r="D20" t="n">
+        <v>440.69</v>
+      </c>
+      <c r="E20" t="n">
+        <v>25740.25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>488.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.99044</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I20" t="n">
+        <v>117.79</v>
+      </c>
+      <c r="J20" t="n">
+        <v>606.49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2.2785</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.7507</v>
+      </c>
+      <c r="D21" t="n">
+        <v>466.37</v>
+      </c>
+      <c r="E21" t="n">
+        <v>27240.16</v>
+      </c>
+      <c r="F21" t="n">
+        <v>517.1799999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.99295</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="I21" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="J21" t="n">
+        <v>603.96</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2.4169</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.8808</v>
+      </c>
+      <c r="D22" t="n">
+        <v>494.71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>28895.46</v>
+      </c>
+      <c r="F22" t="n">
+        <v>548.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.99512</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="J22" t="n">
+        <v>608.76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2.5989</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.0537</v>
+      </c>
+      <c r="D23" t="n">
+        <v>531.97</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31071.32</v>
+      </c>
+      <c r="F23" t="n">
+        <v>589.91</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.99717</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I23" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="J23" t="n">
+        <v>624.8200000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2.8207</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.3263</v>
+      </c>
+      <c r="D24" t="n">
+        <v>577.35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>33722.03</v>
+      </c>
+      <c r="F24" t="n">
+        <v>640.24</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.99868</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="J24" t="n">
+        <v>656.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6797,7 +7542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
